--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -33378,120 +33378,276 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUY TẮC</t>
+          <t xml:space="preserve">BƯỚC / QUY TẮC</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">HƯỚNG DẪN</t>
+          <t xml:space="preserve">AI ĐỌC VÀ LÀM ĐÚNG NGAY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="23" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nguồn sự thật</t>
+          <t xml:space="preserve">0. Đọc nhanh</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan.json là hàng đợi; bảng Excel được tạo lại sau cập nhật G7</t>
+          <t xml:space="preserve">SOP: docs/TITLE-PLAN-1482-SOP.md; không quét lại toàn repo</t>
         </is>
       </c>
     </row>
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEO</t>
+          <t xml:space="preserve">1. Chọn 1–3 đề</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Không sản sinh thêm tiêu đề có cụm Thuê xe máy Hà Nội</t>
+          <t xml:space="preserve">Đọc plan.json hoặc chạy python scripts/title_plan_next.py --limit 3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danh mục</t>
+          <t xml:space="preserve">2. TP không là NT</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dùng Term ID cha con có thật; không tạo chuyên mục mới</t>
+          <t xml:space="preserve">TP-XXXX chỉ là đề tài; chưa Research PASS thì CHƯA được nhận Writer</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51 phường</t>
+          <t xml:space="preserve">3. So trùng</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giữ riêng chiến dịch 51 phường (Term 182) để không trùng</t>
+          <t xml:space="preserve">So URL, slug, intent với WordPress và data/topics.jsonl mới nhất</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nghiên cứu</t>
+          <t xml:space="preserve">4. Chọn danh mục</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tìm và đối chiếu 1-4 trang nguồn cho mỗi tiêu đề</t>
+          <t xml:space="preserve">Đúng Term ID và parent ở data/taxonomy.json; không tạo mục mới</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luật</t>
+          <t xml:space="preserve">5. Đọc nguồn</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bất kỳ khẳng định pháp luật nào đều cần nguồn chính thức</t>
+          <t xml:space="preserve">Tìm 1–4 URL HTTPS thật, ghi chứng cứ nguồn và thời điểm</t>
         </is>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA</t>
+          <t xml:space="preserve">6. Chủ đề luật</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Writer và Publisher giữ QA &gt;=85; không thay đổi các cổng</t>
+          <t xml:space="preserve">GPLX/độ tuổi/luật phải tra nguồn nhà nước đang hiệu lực</t>
         </is>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đã đăng</t>
+          <t xml:space="preserve">7. Giá/xe</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chỉ xác nhận khi ledger có phase VERIFIED và G7 PASS</t>
+          <t xml:space="preserve">NAP, giá, cọc theo data/business-facts.json; thông số theo hãng</t>
         </is>
       </c>
     </row>
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cũ</t>
+          <t xml:space="preserve">8. Research QA</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trước mỗi bài phải rà soát WP và kho chủ đề để chống trùng</t>
+          <t xml:space="preserve">Ứng viên qua Topic Factory/Research QA → NT-XXXXXX PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. W1–W9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim slot auto hợp lệ; không cướp lease hoặc nhận NT chưa PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="23" customHeight="1">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Viết bài</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.600–5.000 từ, intent riêng, 4+ H2, nguồn/internal link thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="23" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11. QA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEO ≥85 + Quality ≥85 + G1–G6 PASS mới đủ điều kiện Publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12. Publisher</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ Publisher được WordPress POST; đúng danh mục, chống trùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="23" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13. Xác minh G7</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ G7 VERIFIED + PASS đầy đủ mới đánh dấu PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="23" customHeight="1">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14. URL sạch</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slug theo tiêu đề; CẤM excel/xlsx/csv/tên file/TP-ID lọt vào URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="23" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15. SEO chính</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không tạo thêm nhiều bài trùng từ khóa thuê xe máy Hà Nội</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="23" customHeight="1">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16. 51 phường</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giữ campaign phường ở Term 182 riêng, tránh nhân bản bài cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="23" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17. Mất mạng</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lưu TP/NT/session/slot/branch/commit/step; resume, không bắt đầu lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="23" customHeight="1">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18. Nguồn sự thật</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excel để xem; plan.json để chọn; Topic Registry và G7 để kiểm trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19. Khi bị chặn</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REVIEW/HOLD/NEEDS_RECONCILE; không bịa QA hoặc POST lại mù</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20. Báo cáo</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TP-ID / NT-ID / QA / WordPress ID / URL công khai / lỗi thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LỆNH NGẮN AI</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đọc SOP; lấy 3 TP; so trùng; nghiên cứu 1–4 nguồn; Research QA; Writer QA; G7</t>
         </is>
       </c>
     </row>

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -243,9 +243,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090001</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4349</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/doi-mau-xe-khi-nhan-cach-xac-nhan-va-xu-ly/</t>
+        </is>
+      </c>
+      <c r="Q2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20T14:25:55.484651+00:00</t>
         </is>
       </c>
     </row>
@@ -310,9 +335,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090002</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4350</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/gia-thue-honda-vision-theo-ngay-khi-phat-sinh-chenh-lech/</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20T14:25:55.484651+00:00</t>
         </is>
       </c>
     </row>
@@ -377,9 +427,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090003</t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4351</t>
+        </is>
+      </c>
+      <c r="P4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-50cc-cho-nguoi-thap-kiem-tra-chong-chan-va-dat-xe/</t>
+        </is>
+      </c>
+      <c r="Q4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20T14:25:55.484651+00:00</t>
         </is>
       </c>
     </row>
@@ -33331,7 +33406,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33341,7 +33416,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -854,9 +854,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090009</t>
+        </is>
+      </c>
+      <c r="O10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4497</t>
+        </is>
+      </c>
+      <c r="P10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/den-pha-xe-may-bi-yeu-khi-nao-nen-thay/</t>
+        </is>
+      </c>
+      <c r="Q10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21T06:05:34.958862+00:00</t>
         </is>
       </c>
     </row>
@@ -33406,7 +33431,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33416,7 +33441,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -1013,9 +1013,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090011</t>
+        </is>
+      </c>
+      <c r="O12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4513</t>
+        </is>
+      </c>
+      <c r="P12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/giay-phep-xe-may-50cc-giay-to-bao-hiem-thuong-nham/</t>
+        </is>
+      </c>
+      <c r="Q12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21T09:05:30.294902+00:00</t>
         </is>
       </c>
     </row>
@@ -1080,9 +1105,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090012</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4514</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bao-tang-phu-nu-viet-nam-lich-trinh-cho-gia-dinh-co-tre/</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21T09:05:30.294902+00:00</t>
         </is>
       </c>
     </row>
@@ -33431,7 +33481,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33441,7 +33491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -4212,9 +4212,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001451</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4667</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/he-thong-den-xe-dap-dien-den-lay-dien-tu-dau-va-thoi-quen-nao-giup-den-ben-hon/</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21T15:18:03.040902+00:00</t>
         </is>
       </c>
     </row>
@@ -8902,9 +8927,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001421</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4665</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/hoa-don-va-chung-tu-thue-xe-may-nen-xin-gi-va-xac-nhan-gi-khi-doi-xe-giua-ky/</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21T15:18:03.040902+00:00</t>
         </is>
       </c>
     </row>
@@ -10108,9 +10158,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001422</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4666</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/goi-thue-xe-may-ba-ngay-doi-chieu-gia-niem-yet-voi-bao-gia-va-hop-dong-thuc-te/</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21T15:18:03.040902+00:00</t>
         </is>
       </c>
     </row>
@@ -33481,7 +33556,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33491,7 +33566,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -7855,9 +7855,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001452</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4670</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dap-dien-leo-doc-cach-doc-mo-men-xoan-cong-suat-va-pin-trong-thong-so-hang/</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21T15:24:08.667229+00:00</t>
         </is>
       </c>
     </row>
@@ -33556,7 +33581,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33566,7 +33591,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -1733,9 +1733,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001511</t>
+        </is>
+      </c>
+      <c r="O22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4681</t>
+        </is>
+      </c>
+      <c r="P22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-50cc-cho-hanh-trinh-ngan-cach-lam-quen-xe-trong-khu-vuc-it-phuong-tien/</t>
+        </is>
+      </c>
+      <c r="Q22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:00:15.209470+00:00</t>
         </is>
       </c>
     </row>
@@ -9580,9 +9605,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M138" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001482</t>
+        </is>
+      </c>
+      <c r="O138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4676</t>
+        </is>
+      </c>
+      <c r="P138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/cach-tra-cuu-van-ban-luat-giao-thong-kiem-tra-hieu-luc-luat-36-2024-va-nghi-dinh-168-2024/</t>
+        </is>
+      </c>
+      <c r="Q138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:00:15.209470+00:00</t>
         </is>
       </c>
     </row>
@@ -10342,9 +10392,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001453</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4675</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dap-dien-dung-pin-lithium-doi-chieu-nhan-ul-2849-ul-2271-voi-thong-tin-hang/</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:00:15.209470+00:00</t>
         </is>
       </c>
     </row>
@@ -11548,9 +11623,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001454</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4677</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dap-dien-sau-khi-di-mua-khi-nao-chi-can-kiem-tra-khi-nao-can-thay-linh-kien/</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:00:15.209470+00:00</t>
         </is>
       </c>
     </row>
@@ -12017,9 +12117,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M174" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001483</t>
+        </is>
+      </c>
+      <c r="O174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4678</t>
+        </is>
+      </c>
+      <c r="P174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/mu-bao-hiem-cho-du-khach-nuoc-ngoai-luat-viet-nam-bat-buoc-gi-va-anh-uc-canada-khuyen-gi/</t>
+        </is>
+      </c>
+      <c r="Q174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:00:15.209470+00:00</t>
         </is>
       </c>
     </row>
@@ -12754,9 +12879,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001455</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4679</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dap-dien-co-ban-dap-cau-tao-co-ban-va-nhung-bo-phan-khong-nen-tu-can-thiep/</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:00:15.209470+00:00</t>
         </is>
       </c>
     </row>
@@ -13223,9 +13373,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M192" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001484</t>
+        </is>
+      </c>
+      <c r="O192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4680</t>
+        </is>
+      </c>
+      <c r="P192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bien-so-xe-may-mau-gi-nen-trang-nen-xanh-tem-xanh-la-va-kich-thuoc-theo-thong-tu-79-2024/</t>
+        </is>
+      </c>
+      <c r="Q192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:00:15.209470+00:00</t>
         </is>
       </c>
     </row>
@@ -33581,7 +33756,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33591,7 +33766,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -1465,9 +1465,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001541</t>
+        </is>
+      </c>
+      <c r="O18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4685</t>
+        </is>
+      </c>
+      <c r="P18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bao-ve-canh-quan-diem-den-mau-ke-hoach-cho-chuyen-di-ngan-tung-buoc/</t>
+        </is>
+      </c>
+      <c r="Q18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:08:33.770618+00:00</t>
         </is>
       </c>
     </row>
@@ -4170,9 +4195,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M58" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001514</t>
+        </is>
+      </c>
+      <c r="O58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4684</t>
+        </is>
+      </c>
+      <c r="P58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-cub-50-dung-di-hoc-nguoi-moi-hay-hieu-nham-gi-ve-so-phanh-va-tuoi-lai/</t>
+        </is>
+      </c>
+      <c r="Q58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:08:33.770618+00:00</t>
         </is>
       </c>
     </row>
@@ -4731,9 +4781,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M66" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001481</t>
+        </is>
+      </c>
+      <c r="O66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4682</t>
+        </is>
+      </c>
+      <c r="P66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/quen-giay-to-xe-may-dien-co-bi-phat-khong-luat-bat-buoc-mang-gi-va-loi-nao-bi-phat/</t>
+        </is>
+      </c>
+      <c r="Q66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:08:33.770618+00:00</t>
         </is>
       </c>
     </row>
@@ -6607,9 +6682,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M94" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001512</t>
+        </is>
+      </c>
+      <c r="O94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="P94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tu-the-lai-xe-50cc-nguoi-moi-hay-hieu-sai-dieu-gi-ve-tay-lung-va-dau-goi/</t>
+        </is>
+      </c>
+      <c r="Q94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:08:33.770618+00:00</t>
         </is>
       </c>
     </row>
@@ -10685,9 +10785,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001571</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4687</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tram-sac-xe-dien-trong-chung-cu-quy-trinh-ra-soat-theo-thong-tu-31-2026-tt-bxd/</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:08:33.770618+00:00</t>
         </is>
       </c>
     </row>
@@ -11288,9 +11413,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M162" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001542</t>
+        </is>
+      </c>
+      <c r="O162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4686</t>
+        </is>
+      </c>
+      <c r="P162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/du-lich-voi-hanh-ly-nhe-gioi-han-sac-du-phong-khi-bay-can-kiem-tra-truoc/</t>
+        </is>
+      </c>
+      <c r="Q162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:08:33.770618+00:00</t>
         </is>
       </c>
     </row>
@@ -33756,7 +33906,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33766,7 +33916,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -519,9 +519,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090004</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4694</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dap-dien-banh-nho-khi-nao-phu-hop-va-luu-y/</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -1264,9 +1289,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001601</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/banh-xeo-mien-tay-an-voi-rau-gi-rau-cuon-nuoc-mam-chua-ngot-va-cu-cai/</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -1624,9 +1674,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001781</t>
+        </is>
+      </c>
+      <c r="O20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4702</t>
+        </is>
+      </c>
+      <c r="P20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/thue-xe-may-khi-doi-lich-bay-nen-uu-tien-yeu-to-nao-neu-chi-dung-vai-ngay/</t>
+        </is>
+      </c>
+      <c r="Q20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -2118,9 +2193,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001572</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4689</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/quan-ly-phu-tai-khi-sac-xe-nguon-rieng-phan-vung-va-so-cho-sac-o-chung-cu/</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -5007,9 +5107,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001602</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4691</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/cao-lau-hoi-an-va-buoi-di-bo-pho-co-nuoc-gieng-ba-le-tro-cu-lao-cham/</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -5476,9 +5601,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001513</t>
+        </is>
+      </c>
+      <c r="O76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4688</t>
+        </is>
+      </c>
+      <c r="P76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/muc-tieu-hao-nhien-lieu-xe-50cc-uu-diem-va-gioi-han-khi-su-dung-hang-ngay/</t>
+        </is>
+      </c>
+      <c r="Q76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -5744,9 +5894,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001751</t>
+        </is>
+      </c>
+      <c r="O80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4701</t>
+        </is>
+      </c>
+      <c r="P80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/kiem-tra-day-dien-xe-may-dien-truoc-khi-di-day-dut-ho-oxi-hoa-va-giac-long/</t>
+        </is>
+      </c>
+      <c r="Q80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -6213,9 +6388,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001603</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4697</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/ve-sinh-khi-an-nem-ran-ha-noi-dau-hieu-ve-dau-ran-nhan-thit-va-cach-bay-ban/</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -7444,9 +7644,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001604</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4698</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tre-nho-uong-ca-phe-trung-duoc-khong-trung-chua-chin-ky-caffeine-do-thay-the/</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -9931,9 +10156,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001605</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4692</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bun-rieu-cua-ha-noi-an-sang-cua-dong-gach-cua-giam-bong-mam-tom-va-rau-kem/</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -11212,9 +11462,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001606</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4693</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/mon-an-cho-phien-vung-cao-thang-co-men-men-pho-chua-va-net-rieng-tung-cho/</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -12493,9 +12768,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M177" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001607</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4699</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/banh-can-da-lat-an-sang-trung-cut-nuoc-xiu-mai-mam-hanh-va-goi-cho-nhom-nho/</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -13682,9 +13982,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M194" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001631</t>
+        </is>
+      </c>
+      <c r="O194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4700</t>
+        </is>
+      </c>
+      <c r="P194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/cao-bang-mua-thac-ban-gioc-lich-trinh-trong-ngay-va-cach-phan-bo-thoi-gian/</t>
+        </is>
+      </c>
+      <c r="Q194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:24:24.525446+00:00</t>
         </is>
       </c>
     </row>
@@ -33906,7 +34231,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33916,7 +34241,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>471</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -1222,9 +1222,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001633</t>
+        </is>
+      </c>
+      <c r="O14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4704</t>
+        </is>
+      </c>
+      <c r="P14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/ba-vi-va-rung-thong-voi-tre-nho-chon-doan-di-bo-ngan-ngay-di-va-gio-nghi/</t>
+        </is>
+      </c>
+      <c r="Q14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -2553,9 +2578,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001637</t>
+        </is>
+      </c>
+      <c r="O32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4706</t>
+        </is>
+      </c>
+      <c r="P32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/hoi-an-luc-sang-som-nhung-loi-len-ke-hoach-thuong-gap-va-cach-tranh/</t>
+        </is>
+      </c>
+      <c r="Q32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -3960,9 +4010,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001721</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4707</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/lan-brt-lang-ha-giang-vo-tu-15-9-2026-xe-may-di-vao-doan-nao-va-gio-nao-dong/</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -8431,9 +8506,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M116" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001752</t>
+        </is>
+      </c>
+      <c r="O116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4712</t>
+        </is>
+      </c>
+      <c r="P116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/kiem-tra-tieng-on-dong-co-dien-tieng-lach-cach-rit-hay-u-cho-biet-dieu-gi/</t>
+        </is>
+      </c>
+      <c r="Q116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -8833,9 +8933,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M122" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001632</t>
+        </is>
+      </c>
+      <c r="O122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4703</t>
+        </is>
+      </c>
+      <c r="P122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/ha-long-ngoai-mua-cao-diem-cach-chon-diem-dung-hop-ly-de-khong-qua-voi/</t>
+        </is>
+      </c>
+      <c r="Q122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -9034,9 +9159,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001726</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4710</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-may-qua-cau-long-bien-gio-dong-nguoi-di-chung-loi-tau-hoa-va-cach-chuan-bi/</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -11395,9 +11545,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M158" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001634</t>
+        </is>
+      </c>
+      <c r="O158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4705</t>
+        </is>
+      </c>
+      <c r="P158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/ha-giang-dau-mua-dong-nhung-trai-nghiem-phu-hop-voi-nguoi-di-lan-dau/</t>
+        </is>
+      </c>
+      <c r="Q158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -12927,9 +13102,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001727</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4711</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tra-diem-ngap-o-ha-noi-khi-mua-lon-ban-do-mua-ngap-ihanoi-bi-an-va-cach-doi-tuyen/</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -16620,9 +16820,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M233" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001722</t>
+        </is>
+      </c>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4708</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tat-may-khi-cho-den-do-tu-may-giay-co-loi-cho-xang-khi-thai-va-khi-nao-chua-nen/</t>
+        </is>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -23856,9 +24081,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M341" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M341" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001723</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4709</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/giao-thong-chiem-bao-nhieu-phan-o-nhiem-khong-khi-ha-noi-60-38-25-hay-23/</t>
+        </is>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T04:38:43.641466+00:00</t>
         </is>
       </c>
     </row>
@@ -34231,7 +34481,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34241,7 +34491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -17046,9 +17046,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M236" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001782</t>
+        </is>
+      </c>
+      <c r="O236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4717</t>
+        </is>
+      </c>
+      <c r="P236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/kiem-tra-phanh-khi-nhan-xe-may-thue-cach-thu-va-viec-can-lam-truoc-khi-dat-coc/</t>
+        </is>
+      </c>
+      <c r="Q236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:01:22.426993+00:00</t>
         </is>
       </c>
     </row>
@@ -30739,9 +30764,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M440" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M440" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001753</t>
+        </is>
+      </c>
+      <c r="O440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4715</t>
+        </is>
+      </c>
+      <c r="P440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dien-rung-giat-khi-khoi-hanh-hoac-van-ga-vi-sao-nen-dung-chay-de-kiem-tra/</t>
+        </is>
+      </c>
+      <c r="Q440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:01:22.426993+00:00</t>
         </is>
       </c>
     </row>
@@ -33151,9 +33201,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M476" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M476" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001754</t>
+        </is>
+      </c>
+      <c r="O476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4716</t>
+        </is>
+      </c>
+      <c r="P476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/lam-kho-xe-may-dien-sau-khi-rua-lau-o-sac-giac-noi-va-cho-bao-lau-moi-sac/</t>
+        </is>
+      </c>
+      <c r="Q476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:01:22.426993+00:00</t>
         </is>
       </c>
     </row>
@@ -34481,7 +34556,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34491,7 +34566,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -28419,9 +28419,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M405" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M405" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N405" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090404</t>
+        </is>
+      </c>
+      <c r="O405" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4756</t>
+        </is>
+      </c>
+      <c r="P405" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bien-bao-khu-vuc-sac-xe-dien-theo-qcvn-32-2026-bct-6-noi-dung-tu-1-7-2027-tram-trong-nha-ngoai-pham-vi/</t>
+        </is>
+      </c>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R405" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:43:08.322426+00:00</t>
         </is>
       </c>
     </row>
@@ -29022,9 +29047,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M414" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M414" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090413</t>
+        </is>
+      </c>
+      <c r="O414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4757</t>
+        </is>
+      </c>
+      <c r="P414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tieng-on-theo-qcvn-26-2025-bnnmt-ban-dem-nha-o-khach-san-45-dba-duong-bo-58-dba-ap-dung-du-tu-1-1-2027/</t>
+        </is>
+      </c>
+      <c r="Q414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:43:08.322426+00:00</t>
         </is>
       </c>
     </row>
@@ -34556,7 +34606,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34566,7 +34616,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -10172,9 +10172,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090138</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4760</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bao-tang-ha-noi-ve-50-000-dong-nghi-thu-hai-mo-toi-thu-sau-bay-bai-gui-xe-chua-350-xe-may/</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:59:45.727920+00:00</t>
         </is>
       </c>
     </row>
@@ -25739,9 +25764,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M365" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M365" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090364</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4761</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/phanh-co-xe-dap-dien-shimano-ghi-khe-ma-phanh-0-2-0-4-mm-tektro-0-3-mm-vi-sao-chinh-hai-ben/</t>
+        </is>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:59:45.727920+00:00</t>
         </is>
       </c>
     </row>
@@ -34606,7 +34656,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34616,7 +34666,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -4554,9 +4554,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M60" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090059</t>
+        </is>
+      </c>
+      <c r="O60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4762</t>
+        </is>
+      </c>
+      <c r="P60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/pin-lfp-vinfast-de-yen-hao-bao-nhieu-khoang-2-duoi-4-moi-thang-hay-duoi-1-5-moi-ngay/</t>
+        </is>
+      </c>
+      <c r="Q60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T07:14:07.953143+00:00</t>
         </is>
       </c>
     </row>
@@ -27732,9 +27757,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M394" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M394" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090393</t>
+        </is>
+      </c>
+      <c r="O394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4763</t>
+        </is>
+      </c>
+      <c r="P394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/ha-noi-giap-5-tinh-nao-sau-sap-nhap-thai-nguyen-phu-tho-bac-ninh-hung-yen-va-ninh-binh/</t>
+        </is>
+      </c>
+      <c r="Q394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T07:14:07.953143+00:00</t>
         </is>
       </c>
     </row>
@@ -34656,7 +34706,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34666,7 +34716,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -17590,9 +17590,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M243" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090242</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4766</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/khu-sac-xe-dien-tap-trung-trong-nha-khong-co-giai-phap-ngan-chay-phat-40-50-trieu-nd-106-2025/</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T07:27:53.401739+00:00</t>
         </is>
       </c>
     </row>
@@ -34706,7 +34731,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34716,7 +34741,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -5366,9 +5366,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090070</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4769</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/duong-danh-rieng-cho-xe-buyt-nghi-dinh-168-2024-neu-o-dieu-6-va-8-xe-may-ap-dung-dieu-nao/</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T09:30:34.640991+00:00</t>
         </is>
       </c>
     </row>
@@ -19290,9 +19315,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M268" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001661</t>
+        </is>
+      </c>
+      <c r="O268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4768</t>
+        </is>
+      </c>
+      <c r="P268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/doi-lich-vi-chuyen-bay-tre-hang-phai-ho-tro-gi-theo-moc-gio-va-khach-nen-lam-gi/</t>
+        </is>
+      </c>
+      <c r="Q268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T09:30:34.640991+00:00</t>
         </is>
       </c>
     </row>
@@ -20898,9 +20948,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M292" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090291</t>
+        </is>
+      </c>
+      <c r="O292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4770</t>
+        </is>
+      </c>
+      <c r="P292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bien-p-111a-cam-xe-gan-may-p-104-cam-xe-may-va-p-103a-cam-xe-o-to-xe-50cc-bi-cam-o-bien-nao/</t>
+        </is>
+      </c>
+      <c r="Q292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T09:30:34.640991+00:00</t>
         </is>
       </c>
     </row>
@@ -34731,7 +34806,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34741,7 +34816,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -20546,9 +20546,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M286" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001665</t>
+        </is>
+      </c>
+      <c r="O286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4771</t>
+        </is>
+      </c>
+      <c r="P286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/du-tru-phi-phat-sinh-nhung-khoan-nguoi-di-du-lich-tu-tuc-lan-dau-hay-bo-sot/</t>
+        </is>
+      </c>
+      <c r="Q286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T09:37:53.661776+00:00</t>
         </is>
       </c>
     </row>
@@ -34806,7 +34831,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34816,7 +34841,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -27681,9 +27681,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M391" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M391" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090390</t>
+        </is>
+      </c>
+      <c r="O391" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4773</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/duong-ven-ho-tay-khoi-cong-28-8-2026-cai-tao-13-5-km-doan-quang-an-du-kien-xong-quy-iii-2027/</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T09:58:19.998082+00:00</t>
         </is>
       </c>
     </row>
@@ -31935,9 +31960,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M453" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M453" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N453" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090452</t>
+        </is>
+      </c>
+      <c r="O453" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4775</t>
+        </is>
+      </c>
+      <c r="P453" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/phat-nguoi-den-sau-khi-tra-xe-may-thue-thoi-hieu-1-nam-tinh-tu-luc-camera-ghi-hinh/</t>
+        </is>
+      </c>
+      <c r="Q453" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R453" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T09:58:19.998082+00:00</t>
         </is>
       </c>
     </row>
@@ -34831,7 +34881,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34841,7 +34891,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -21534,9 +21534,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M300" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090299</t>
+        </is>
+      </c>
+      <c r="O300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4776</t>
+        </is>
+      </c>
+      <c r="P300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/mat-giay-phep-lai-xe-con-han-cap-lai-theo-dieu-20-thong-tu-108-2026-hai-truong-hop-bi-tu-choi/</t>
+        </is>
+      </c>
+      <c r="Q300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T10:02:23.902748+00:00</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34906,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34891,7 +34916,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -12951,9 +12951,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001635</t>
+        </is>
+      </c>
+      <c r="O176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4777</t>
+        </is>
+      </c>
+      <c r="P176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/da-lat-mua-kho-meo-danh-cho-khach-lan-dau-tu-to-chuc-chuyen-di/</t>
+        </is>
+      </c>
+      <c r="Q176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T10:12:35.697575+00:00</t>
         </is>
       </c>
     </row>
@@ -14031,9 +14056,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001691</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4778</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/quan-sat-truoc-khi-mo-cua-xe-dieu-19-luat-36-2024-muc-phat-va-tranh-va-xe-may/</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T10:12:35.697575+00:00</t>
         </is>
       </c>
     </row>
@@ -34906,7 +34956,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34916,7 +34966,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -2804,9 +2804,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001724</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4785</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/gui-xe-o-ha-noi-khong-tien-mat-tu-1-7-2026-quet-ma-qr-theo-menh-gia-in-san/</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T10:22:05.343371+00:00</t>
         </is>
       </c>
     </row>
@@ -7861,9 +7886,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001662</t>
+        </is>
+      </c>
+      <c r="O106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4783</t>
+        </is>
+      </c>
+      <c r="P106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/du-lich-hai-ngay-mot-dem-xuat-phat-buoi-sang-hay-buoi-chieu-hop-ly-hon/</t>
+        </is>
+      </c>
+      <c r="Q106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T10:22:05.343371+00:00</t>
         </is>
       </c>
     </row>
@@ -15538,9 +15588,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M212" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001636</t>
+        </is>
+      </c>
+      <c r="O212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4782</t>
+        </is>
+      </c>
+      <c r="P212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/mai-chau-vao-cuoi-tuan-dieu-nen-tim-hieu-truoc-de-ton-trong-van-hoa-dia-phuong/</t>
+        </is>
+      </c>
+      <c r="Q212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T10:22:05.343371+00:00</t>
         </is>
       </c>
     </row>
@@ -23954,9 +24029,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M335" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M335" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001692</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4784</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/qua-doan-duong-dang-sua-bang-xe-may-bien-tam-toc-do-tam-thep-va-soi-truot/</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T10:22:05.343371+00:00</t>
         </is>
       </c>
     </row>
@@ -34956,7 +35056,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -34966,7 +35066,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -1473,9 +1473,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-001725</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4791</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/cam-duong-de-thi-cong-o-ha-noi-doc-thong-bao-phan-luong-va-chon-duong-vong/</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T10:27:40.040192+00:00</t>
         </is>
       </c>
     </row>
@@ -35056,7 +35081,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35066,7 +35091,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -22379,9 +22379,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M310" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M310" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090309</t>
+        </is>
+      </c>
+      <c r="O310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4824</t>
+        </is>
+      </c>
+      <c r="P310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/phanh-va-lop-xe-50cc-sym-priti-50-dia-truoc-vanh-10-inch-elegant-50-tang-trong-vanh-17-inch/</t>
+        </is>
+      </c>
+      <c r="Q310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T11:47:12.687443+00:00</t>
         </is>
       </c>
     </row>
@@ -26206,9 +26231,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M366" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M366" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090365</t>
+        </is>
+      </c>
+      <c r="O366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4823</t>
+        </is>
+      </c>
+      <c r="P366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/pin-dat-bike-25-nam-tuong-duong-350-000-km-hay-50-000-km-con-80-hay-70-dung-luong/</t>
+        </is>
+      </c>
+      <c r="Q366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T11:47:12.687443+00:00</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35131,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35091,7 +35141,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -6161,9 +6161,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090080</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4826</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tram-sac-ngoai-troi-ngap-nuoc-thi-sao-qcvn-32-2026-bct-tu-1-7-2027-buoc-ngat-dien-thoat-nuoc/</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T11:54:26.896193+00:00</t>
         </is>
       </c>
     </row>
@@ -35131,7 +35156,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35141,7 +35166,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -17162,9 +17162,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M234" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090233</t>
+        </is>
+      </c>
+      <c r="O234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4827</t>
+        </is>
+      </c>
+      <c r="P234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tui-ni-long-o-cho-ha-noi-het-mien-phi-tu-1-1-2026-hay-1-1-2027-khong-luu-hanh-tu-1-1-2028/</t>
+        </is>
+      </c>
+      <c r="Q234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T12:01:13.163812+00:00</t>
         </is>
       </c>
     </row>
@@ -35156,7 +35181,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35166,7 +35191,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -17547,9 +17547,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M239" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090238</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4829</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dap-dien-di-hoc-cho-may-nguoi-dieu-31-cho-1-nguoi-tre-duoi-7-tuoi-thi-2-drgnfly-02-nguoi/</t>
+        </is>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T14:56:51.702187+00:00</t>
         </is>
       </c>
     </row>
@@ -35181,7 +35206,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35191,7 +35216,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -6521,9 +6521,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M86" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090085</t>
+        </is>
+      </c>
+      <c r="O86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4840</t>
+        </is>
+      </c>
+      <c r="P86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/ve-hai-van-quan-70-000-dong-tu-2-6-2026-tre-em-duoi-13-tuoi-hay-duoi-1-2-m-duoc-mien-phi/</t>
+        </is>
+      </c>
+      <c r="Q86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T15:24:43.231174+00:00</t>
         </is>
       </c>
     </row>
@@ -35206,7 +35231,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35216,7 +35241,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -2109,9 +2109,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090024</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4881</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dap-dien-bosch-bao-loi-503-504-khe-nam-cham-cam-bien-toc-do-2-8-mm-hay-5-17-mm/</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -9853,9 +9878,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M132" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090131</t>
+        </is>
+      </c>
+      <c r="O132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4888</t>
+        </is>
+      </c>
+      <c r="P132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/nhiet-do-pin-vinfast-amio-va-evo-lite-xe-giam-hieu-nang-tren-45-c-pin-ngung-o-65-c-hay-60-c/</t>
+        </is>
+      </c>
+      <c r="Q132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -13553,9 +13603,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M182" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090181</t>
+        </is>
+      </c>
+      <c r="O182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4889</t>
+        </is>
+      </c>
+      <c r="P182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/nhom-ban-thue-xe-may-mot-nguoi-dung-ten-hay-cung-ky-dieu-287-va-288-bo-luat-dan-su-noi-gi/</t>
+        </is>
+      </c>
+      <c r="Q182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -15328,9 +15403,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090206</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4890</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tu-doi-pin-xe-may-dien-o-chung-cu-ngoai-troi-3-m-trong-nha-cach-thang-6-m-tran-18-100-kwh/</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -18828,9 +18928,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M257" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090256</t>
+        </is>
+      </c>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4891</t>
+        </is>
+      </c>
+      <c r="P257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-dap-dien-cho-hang-luat-36-2024-gioi-han-1-3-than-xe-1-m-truoc-sau-va-0-4-m-moi-ben-banh/</t>
+        </is>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -19724,9 +19849,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M270" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090269</t>
+        </is>
+      </c>
+      <c r="O270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4892</t>
+        </is>
+      </c>
+      <c r="P270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/du-lich-bang-xe-dap-dien-thai-bao-nhieu-co2-moi-km-luoi-dien-0-6187-tco2-mwh-pin-640-wh/</t>
+        </is>
+      </c>
+      <c r="Q270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -19925,9 +20075,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M273" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090272</t>
+        </is>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4893</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/dat-coc-thue-xe-may-bang-usd-han-che-ngoai-hoi-chuyen-tu-dieu-22-sang-dieu-31a-ngay-1-12-2026/</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -26557,9 +26732,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M369" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M369" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090368</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4894</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tram-sac-cong-cong-khong-duoc-can-loi-thoat-nan-xe-chua-chay-nguoi-di-bo-qcvn-32-2026-bct/</t>
+        </is>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -33608,9 +33808,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M472" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M472" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090471</t>
+        </is>
+      </c>
+      <c r="O472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4895</t>
+        </is>
+      </c>
+      <c r="P472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/cho-vali-20-inch-bang-xe-ga-50cc-sym-priti-50-ghi-san-de-chan-264-mm-tai-130-kg-2-nguoi/</t>
+        </is>
+      </c>
+      <c r="Q472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35456,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35241,7 +35466,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>418</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -9518,9 +9518,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090126</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5020</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/sym-angel-110-priti-125-va-tpbw-125-mau-nao-ghi-smartkey-cong-usb-cop-22-5-l-va-phanh-cbs/</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T20:40:31.742795+00:00</t>
         </is>
       </c>
     </row>
@@ -35456,7 +35481,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35466,7 +35491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-01-494.xlsx
@@ -20033,9 +20033,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M272" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090271</t>
+        </is>
+      </c>
+      <c r="O272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5032</t>
+        </is>
+      </c>
+      <c r="P272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/chia-khoa-du-phong-xe-may-thue-co-phai-vat-phu-theo-dieu-110-mat-chia-thi-den-theo-dieu-479/</t>
+        </is>
+      </c>
+      <c r="Q272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T21:03:04.092091+00:00</t>
         </is>
       </c>
     </row>
@@ -35481,7 +35506,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -35491,7 +35516,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
